--- a/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYdyn.xlsx
+++ b/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYdyn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DUHad\Documents\DataXlCalcNet\DataExamples\MainExamples\Workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBF880A-8615-4998-B08F-A2728B617D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F378DD-D435-4EDE-BDB6-0A3B5694FC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-83" yWindow="0" windowWidth="18923" windowHeight="19928" xr2:uid="{D1AD1D0F-8D38-4AC9-9C06-62EFBEFC0648}"/>
   </bookViews>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10651DF-E94E-4B0F-AFE7-F3473E013BA6}">
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.59765625" customWidth="1"/>
@@ -568,8 +568,8 @@
         <v>mu0:</v>
       </c>
       <c r="B4" s="2" t="str">
-        <f>"1.0"</f>
-        <v>1.0</v>
+        <f>"1.1"</f>
+        <v>1.1</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -736,344 +736,344 @@
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
     </row>
-    <row r="12" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="5" t="str" cm="1">
-        <f t="array" ref="A12:E31">_xll.CPY_0(_xlfn.TEXTJOIN(" ",1,"from A06_UserlibExamplesPython.B29_InferentialStatistics.C01_BasicTests1Sample import D01_StudentT_PValues $n result=D01_StudentT_PValues.stats_student_t_1sample_test(n=",B3,", mu0=",B4,", mean=",B5,",  std=",B6,", alpha=", B7, B8, ")",""))</f>
+    <row r="11" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="str" cm="1">
+        <f t="array" ref="A11:E30">_xll.CPY_0(_xlfn.TEXTJOIN(" ",1,"from A06_UserlibExamplesPython.B29_InferentialStatistics.C01_BasicTests1Sample import D01_StudentT_PValues $n result=D01_StudentT_PValues.stats_student_t_1sample_test(n=",B3,", mu0=",B4,", mean=",B5,",  std=",B6,", alpha=", B7, B8, ")",""))</f>
         <v>Item</v>
       </c>
-      <c r="B12" s="6" t="str">
+      <c r="B11" s="6" t="str">
         <v>Group1</v>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C11" s="6" t="str">
         <v>Group2</v>
       </c>
-      <c r="D12" s="6" t="str">
+      <c r="D11" s="6" t="str">
         <v>Group3</v>
       </c>
-      <c r="E12" s="6" t="str">
+      <c r="E11" s="6" t="str">
         <v>Group4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="str">
+        <v>n</v>
+      </c>
+      <c r="B12" s="8" t="str">
+        <v>10.0</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <v>20.0</v>
+      </c>
+      <c r="D12" s="8" t="str">
+        <v>30.0</v>
+      </c>
+      <c r="E12" s="8" t="str">
+        <v>30.0</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="str">
-        <v>n</v>
+        <v>mean</v>
       </c>
       <c r="B13" s="8" t="str">
-        <v>10.0</v>
+        <v>4.5</v>
       </c>
       <c r="C13" s="8" t="str">
-        <v>20.0</v>
+        <v>4.7</v>
       </c>
       <c r="D13" s="8" t="str">
-        <v>30.0</v>
+        <v>4.7</v>
       </c>
       <c r="E13" s="8" t="str">
-        <v>30.0</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="str">
-        <v>mean</v>
+        <v>μ0</v>
       </c>
       <c r="B14" s="8" t="str">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="C14" s="8" t="str">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="D14" s="8" t="str">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="E14" s="8" t="str">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="str">
-        <v>μ0</v>
+        <v>stdev</v>
       </c>
       <c r="B15" s="8" t="str">
         <v>1.0</v>
       </c>
       <c r="C15" s="8" t="str">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D15" s="8" t="str">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E15" s="8" t="str">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="str">
-        <v>stdev</v>
+        <v>alpha</v>
       </c>
       <c r="B16" s="8" t="str">
-        <v>1.0</v>
+        <v>0.05</v>
       </c>
       <c r="C16" s="8" t="str">
-        <v>2.0</v>
+        <v>0.05</v>
       </c>
       <c r="D16" s="8" t="str">
-        <v>3.0</v>
+        <v>0.05</v>
       </c>
       <c r="E16" s="8" t="str">
-        <v>4.0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="str">
-        <v>alpha</v>
+        <v>degrees of freedom</v>
       </c>
       <c r="B17" s="8" t="str">
-        <v>0.05</v>
+        <v>9.0</v>
       </c>
       <c r="C17" s="8" t="str">
-        <v>0.05</v>
+        <v>19.0</v>
       </c>
       <c r="D17" s="8" t="str">
-        <v>0.05</v>
+        <v>29.0</v>
       </c>
       <c r="E17" s="8" t="str">
-        <v>0.05</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="str">
-        <v>degrees of freedom</v>
+        <v>difference of means</v>
       </c>
       <c r="B18" s="8" t="str">
-        <v>9.0</v>
+        <v>3.4</v>
       </c>
       <c r="C18" s="8" t="str">
-        <v>19.0</v>
+        <v>3.6</v>
       </c>
       <c r="D18" s="8" t="str">
-        <v>29.0</v>
+        <v>3.6</v>
       </c>
       <c r="E18" s="8" t="str">
-        <v>29.0</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="str">
-        <v>difference of means</v>
+        <v>rho-tilde = (mean-mu0)/stdev</v>
       </c>
       <c r="B19" s="8" t="str">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="C19" s="8" t="str">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="D19" s="8" t="str">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="E19" s="8" t="str">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="str">
-        <v>rho-tilde = (mean-mu0)/stdev</v>
+        <v>t-value (=delta)</v>
       </c>
       <c r="B20" s="8" t="str">
-        <v>3.5</v>
+        <v>10.75174404</v>
       </c>
       <c r="C20" s="8" t="str">
-        <v>1.85</v>
+        <v>8.049844719</v>
       </c>
       <c r="D20" s="8" t="str">
-        <v>1.233333333</v>
+        <v>6.57267069</v>
       </c>
       <c r="E20" s="8" t="str">
-        <v>0.925</v>
+        <v>4.929503018</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="str">
-        <v>t-value (=delta)</v>
+        <v>t(1-alpha, 1-sided)</v>
       </c>
       <c r="B21" s="8" t="str">
-        <v>11.06797181</v>
+        <v>1.833112933</v>
       </c>
       <c r="C21" s="8" t="str">
-        <v>8.273451517</v>
+        <v>1.729132812</v>
       </c>
       <c r="D21" s="8" t="str">
-        <v>6.755244876</v>
+        <v>1.699127027</v>
       </c>
       <c r="E21" s="8" t="str">
-        <v>5.066433657</v>
+        <v>1.699127027</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="str">
-        <v>t(1-alpha, 1-sided)</v>
+        <v>t(1-alpha, 2-sided)</v>
       </c>
       <c r="B22" s="8" t="str">
-        <v>1.833112933</v>
+        <v>2.262157163</v>
       </c>
       <c r="C22" s="8" t="str">
-        <v>1.729132812</v>
+        <v>2.093024054</v>
       </c>
       <c r="D22" s="8" t="str">
-        <v>1.699127027</v>
+        <v>2.045229642</v>
       </c>
       <c r="E22" s="8" t="str">
-        <v>1.699127027</v>
+        <v>2.045229642</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="str">
-        <v>t(1-alpha, 2-sided)</v>
+        <v>test, p-value (H01: μ1 ≥ μ0)</v>
       </c>
       <c r="B23" s="8" t="str">
-        <v>2.262157163</v>
+        <v>0.9999990244</v>
       </c>
       <c r="C23" s="8" t="str">
-        <v>2.093024054</v>
+        <v>0.9999999236</v>
       </c>
       <c r="D23" s="8" t="str">
-        <v>2.045229642</v>
+        <v>0.9999998323</v>
       </c>
       <c r="E23" s="8" t="str">
-        <v>2.045229642</v>
+        <v>0.9999845715</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="str">
-        <v>test, p-value (H01: μ1 ≥ μ0)</v>
+        <v>test, p-value (H02: μ1 ≤ μ0)</v>
       </c>
       <c r="B24" s="8" t="str">
-        <v>0.9999992358</v>
+        <v>9.755717864e-7</v>
       </c>
       <c r="C24" s="8" t="str">
-        <v>0.9999999493</v>
+        <v>7.640342437e-8</v>
       </c>
       <c r="D24" s="8" t="str">
-        <v>0.9999998973</v>
+        <v>1.676890183e-7</v>
       </c>
       <c r="E24" s="8" t="str">
-        <v>0.9999894555</v>
+        <v>1.542852988e-5</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="str">
-        <v>test, p-value (H02: μ1 ≤ μ0)</v>
+        <v>test, p-value (H03: μ1 = μ0)</v>
       </c>
       <c r="B25" s="8" t="str">
-        <v>7.642011941e-7</v>
+        <v>1.951143573e-6</v>
       </c>
       <c r="C25" s="8" t="str">
-        <v>5.068466643e-8</v>
+        <v>1.528068487e-7</v>
       </c>
       <c r="D25" s="8" t="str">
-        <v>1.026891697e-7</v>
+        <v>3.353780366e-7</v>
       </c>
       <c r="E25" s="8" t="str">
-        <v>1.05444532e-5</v>
+        <v>3.085705976e-5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="str">
-        <v>test, p-value (H03: μ1 = μ0)</v>
+        <v>μ1 - μ0, CI upper limit (1-sided)</v>
       </c>
       <c r="B26" s="8" t="str">
-        <v>1.528402388e-6</v>
+        <v>3.979681208</v>
       </c>
       <c r="C26" s="8" t="str">
-        <v>1.013693329e-7</v>
+        <v>4.373291702</v>
       </c>
       <c r="D26" s="8" t="str">
-        <v>2.053783395e-7</v>
+        <v>4.5306502</v>
       </c>
       <c r="E26" s="8" t="str">
-        <v>2.108890639e-5</v>
+        <v>4.840866934</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="str">
-        <v>μ1 - μ0, CI upper limit (1-sided)</v>
+        <v>μ1 - μ0, CI lower limit (1-sided)</v>
       </c>
       <c r="B27" s="8" t="str">
-        <v>4.079681208</v>
+        <v>2.820318792</v>
       </c>
       <c r="C27" s="8" t="str">
-        <v>4.473291702</v>
+        <v>2.826708298</v>
       </c>
       <c r="D27" s="8" t="str">
-        <v>4.630650201</v>
+        <v>2.6693498</v>
       </c>
       <c r="E27" s="8" t="str">
-        <v>4.940866934</v>
+        <v>2.359133066</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="str">
-        <v>μ1 - μ0, CI lower limit (1-sided)</v>
+        <v>μ1 - μ0, CI upper limit (2-sided)</v>
       </c>
       <c r="B28" s="8" t="str">
-        <v>2.920318792</v>
+        <v>4.115356906</v>
       </c>
       <c r="C28" s="8" t="str">
-        <v>2.926708298</v>
+        <v>4.536028813</v>
       </c>
       <c r="D28" s="8" t="str">
-        <v>2.7693498</v>
+        <v>4.72021841</v>
       </c>
       <c r="E28" s="8" t="str">
-        <v>2.459133066</v>
+        <v>5.093624547</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="str">
-        <v>μ1 - μ0, CI upper limit (2-sided)</v>
+        <v>μ1 - μ0, CI lower limit (2-sided)</v>
       </c>
       <c r="B29" s="8" t="str">
-        <v>4.215356906</v>
+        <v>2.684643094</v>
       </c>
       <c r="C29" s="8" t="str">
-        <v>4.636028813</v>
+        <v>2.663971187</v>
       </c>
       <c r="D29" s="8" t="str">
-        <v>4.82021841</v>
+        <v>2.47978159</v>
       </c>
       <c r="E29" s="8" t="str">
-        <v>5.193624547</v>
+        <v>2.106375453</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="str">
-        <v>μ1 - μ0, CI lower limit (2-sided)</v>
+        <v>μ1 - μ0, CI-length (2-sided)</v>
       </c>
       <c r="B30" s="8" t="str">
-        <v>2.784643094</v>
+        <v>1.430713812</v>
       </c>
       <c r="C30" s="8" t="str">
-        <v>2.763971187</v>
+        <v>1.872057626</v>
       </c>
       <c r="D30" s="8" t="str">
-        <v>2.57978159</v>
+        <v>2.24043682</v>
       </c>
       <c r="E30" s="8" t="str">
-        <v>2.206375453</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A31" s="7" t="str">
-        <v>μ1 - μ0, CI-length (2-sided)</v>
-      </c>
-      <c r="B31" s="8" t="str">
-        <v>1.430713812</v>
-      </c>
-      <c r="C31" s="8" t="str">
-        <v>1.872057626</v>
-      </c>
-      <c r="D31" s="8" t="str">
-        <v>2.240436821</v>
-      </c>
-      <c r="E31" s="8" t="str">
         <v>2.987249094</v>
       </c>
     </row>

--- a/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYdyn.xlsx
+++ b/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYdyn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DUHad\Documents\DataXlCalcNet\DataExamples\MainExamples\Workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F378DD-D435-4EDE-BDB6-0A3B5694FC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB08F05F-AFDB-41C0-8930-93BAD4DDCCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-83" yWindow="0" windowWidth="18923" windowHeight="19928" xr2:uid="{D1AD1D0F-8D38-4AC9-9C06-62EFBEFC0648}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -738,7 +738,7 @@
     </row>
     <row r="11" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="str" cm="1">
-        <f t="array" ref="A11:E30">_xll.CPY_0(_xlfn.TEXTJOIN(" ",1,"from A06_UserlibExamplesPython.B29_InferentialStatistics.C01_BasicTests1Sample import D01_StudentT_PValues $n result=D01_StudentT_PValues.stats_student_t_1sample_test(n=",B3,", mu0=",B4,", mean=",B5,",  std=",B6,", alpha=", B7, B8, ")",""))</f>
+        <f t="array" ref="A11:E30">_xll.CPY_0(_xlfn.TEXTJOIN(" ",1,"from A06_UserlibExamplesPython.B29_InferentialStatistics.C01_BasicTests1Sample import D01_StudentT_PValues $n importlib.reload(D01_StudentT_PValues) $n  result=D01_StudentT_PValues.stats_student_t_1sample_test(n=",B3,", mu0=",B4,", mean=",B5,",  std=",B6,", alpha=", B7, B8, ")",""))</f>
         <v>Item</v>
       </c>
       <c r="B11" s="6" t="str">
